--- a/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
@@ -468,7 +468,7 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>0.02263239999999976</v>
+        <v>0.02263239999999975</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -567,7 +567,7 @@
         <v>11</v>
       </c>
       <c r="C14">
-        <v>0.03052600000000001</v>
+        <v>0.03052600000000002</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -633,7 +633,7 @@
         <v>11</v>
       </c>
       <c r="C20">
-        <v>0.02636791788961459</v>
+        <v>0.0263679178896146</v>
       </c>
     </row>
     <row r="21" spans="1:3">

--- a/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
@@ -567,7 +567,7 @@
         <v>11</v>
       </c>
       <c r="C14">
-        <v>0.03052600000000002</v>
+        <v>0.03052600000000003</v>
       </c>
     </row>
     <row r="15" spans="1:3">

--- a/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
   <si>
     <t>Model</t>
   </si>
@@ -50,12 +50,6 @@
   </si>
   <si>
     <t>Popular Vote</t>
-  </si>
-  <si>
-    <t>House Buckets</t>
-  </si>
-  <si>
-    <t>Senate Buckets</t>
   </si>
 </sst>
 </file>
@@ -413,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -454,197 +448,65 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>5.5407</v>
+        <v>0.02177959999999972</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
       <c r="C5">
-        <v>0.02263239999999975</v>
+        <v>0.04010000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>1.04055</v>
+        <v>0.01193820542365915</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>6.4</v>
+        <v>0.02858919999999997</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8">
-        <v>0.04010000000000001</v>
+        <v>0.02235382843390595</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9">
-        <v>1.3375</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10">
-        <v>5.24749619700716</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11">
-        <v>0.01193820542365915</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12">
-        <v>1.038416113387647</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13">
-        <v>5.785300000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14">
-        <v>0.03052600000000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15">
-        <v>1.1625</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16">
-        <v>5.24749619700716</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17">
-        <v>0.01634036927331421</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18">
-        <v>1.038416113387647</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19">
-        <v>5.62870877099317</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20">
-        <v>0.0263679178896146</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21">
-        <v>1.100328149530577</v>
+        <v>0.02470934877672151</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
@@ -506,7 +506,7 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>0.02470934877672151</v>
+        <v>0.0247093487767215</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
@@ -506,7 +506,7 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>0.0247093487767215</v>
+        <v>0.02470934877672151</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
@@ -451,7 +451,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>0.02177959999999972</v>
+        <v>0.02177959999999971</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -484,7 +484,7 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>0.02858919999999997</v>
+        <v>0.02858919999999996</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -506,7 +506,7 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>0.02470934877672151</v>
+        <v>0.0247093487767215</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
@@ -484,7 +484,7 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>0.02858919999999996</v>
+        <v>0.02858919999999997</v>
       </c>
     </row>
     <row r="8" spans="1:3">

--- a/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
@@ -451,7 +451,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>0.02177959999999971</v>
+        <v>0.02177959999999972</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -506,7 +506,7 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>0.0247093487767215</v>
+        <v>0.02470934877672151</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Summary_v12.xlsx
@@ -506,7 +506,7 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>0.02470934877672151</v>
+        <v>0.02470934877672152</v>
       </c>
     </row>
   </sheetData>
